--- a/artfynd/A 42078-2019 artfynd.xlsx
+++ b/artfynd/A 42078-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42078-2019 artfynd.xlsx
+++ b/artfynd/A 42078-2019 artfynd.xlsx
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118637394</v>
+        <v>118637407</v>
       </c>
       <c r="B6" t="n">
-        <v>78573</v>
+        <v>79565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,25 +1142,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542982</v>
+        <v>542937</v>
       </c>
       <c r="R6" t="n">
-        <v>6985997</v>
+        <v>6985813</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118637407</v>
+        <v>118637398</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>90451</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542937</v>
+        <v>543124</v>
       </c>
       <c r="R7" t="n">
-        <v>6985813</v>
+        <v>6986062</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118637399</v>
+        <v>118637397</v>
       </c>
       <c r="B8" t="n">
-        <v>90522</v>
+        <v>90518</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543124</v>
+        <v>542989</v>
       </c>
       <c r="R8" t="n">
-        <v>6986145</v>
+        <v>6985815</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118637396</v>
+        <v>118637406</v>
       </c>
       <c r="B9" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,25 +1448,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543007</v>
+        <v>542918</v>
       </c>
       <c r="R9" t="n">
-        <v>6985892</v>
+        <v>6985972</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118637395</v>
+        <v>118637408</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543004</v>
+        <v>542882</v>
       </c>
       <c r="R10" t="n">
-        <v>6985918</v>
+        <v>6985834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118637406</v>
+        <v>118637395</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,25 +1652,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542918</v>
+        <v>543004</v>
       </c>
       <c r="R11" t="n">
-        <v>6985972</v>
+        <v>6985918</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118637397</v>
+        <v>118637394</v>
       </c>
       <c r="B13" t="n">
-        <v>90518</v>
+        <v>78573</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,25 +1856,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6450</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542989</v>
+        <v>542982</v>
       </c>
       <c r="R13" t="n">
-        <v>6985815</v>
+        <v>6985997</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118637401</v>
+        <v>118637396</v>
       </c>
       <c r="B15" t="n">
-        <v>90504</v>
+        <v>79565</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543069</v>
+        <v>543007</v>
       </c>
       <c r="R15" t="n">
-        <v>6986146</v>
+        <v>6985892</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118637402</v>
+        <v>118637401</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,21 +2166,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543018</v>
+        <v>543069</v>
       </c>
       <c r="R16" t="n">
-        <v>6986137</v>
+        <v>6986146</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118637398</v>
+        <v>118637399</v>
       </c>
       <c r="B17" t="n">
-        <v>90451</v>
+        <v>90522</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,21 +2268,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,7 +2295,7 @@
         <v>543124</v>
       </c>
       <c r="R17" t="n">
-        <v>6986062</v>
+        <v>6986145</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118637408</v>
+        <v>118637402</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2366,25 +2366,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542882</v>
+        <v>543018</v>
       </c>
       <c r="R18" t="n">
-        <v>6985834</v>
+        <v>6986137</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 42078-2019 artfynd.xlsx
+++ b/artfynd/A 42078-2019 artfynd.xlsx
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118637407</v>
+        <v>118637398</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>90451</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,21 +1146,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542937</v>
+        <v>543124</v>
       </c>
       <c r="R6" t="n">
-        <v>6985813</v>
+        <v>6986062</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118637398</v>
+        <v>118637407</v>
       </c>
       <c r="B7" t="n">
-        <v>90451</v>
+        <v>79565</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543124</v>
+        <v>542937</v>
       </c>
       <c r="R7" t="n">
-        <v>6986062</v>
+        <v>6985813</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 42078-2019 artfynd.xlsx
+++ b/artfynd/A 42078-2019 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118637405</v>
+        <v>118637399</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>90522</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,25 +1040,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542943</v>
+        <v>543124</v>
       </c>
       <c r="R5" t="n">
-        <v>6986128</v>
+        <v>6986145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118637398</v>
+        <v>118637394</v>
       </c>
       <c r="B6" t="n">
-        <v>90451</v>
+        <v>78573</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,25 +1142,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>6450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543124</v>
+        <v>542982</v>
       </c>
       <c r="R6" t="n">
-        <v>6986062</v>
+        <v>6985997</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118637407</v>
+        <v>118637405</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1244,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542937</v>
+        <v>542943</v>
       </c>
       <c r="R7" t="n">
-        <v>6985813</v>
+        <v>6986128</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118637397</v>
+        <v>118637396</v>
       </c>
       <c r="B8" t="n">
-        <v>90518</v>
+        <v>79565</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542989</v>
+        <v>543007</v>
       </c>
       <c r="R8" t="n">
-        <v>6985815</v>
+        <v>6985892</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118637406</v>
+        <v>118637401</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,25 +1448,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542918</v>
+        <v>543069</v>
       </c>
       <c r="R9" t="n">
-        <v>6985972</v>
+        <v>6986146</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118637408</v>
+        <v>118637407</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542882</v>
+        <v>542937</v>
       </c>
       <c r="R10" t="n">
-        <v>6985834</v>
+        <v>6985813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118637404</v>
+        <v>118637402</v>
       </c>
       <c r="B12" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,25 +1754,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542973</v>
+        <v>543018</v>
       </c>
       <c r="R12" t="n">
-        <v>6986138</v>
+        <v>6986137</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118637394</v>
+        <v>118637408</v>
       </c>
       <c r="B13" t="n">
-        <v>78573</v>
+        <v>97846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,25 +1856,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542982</v>
+        <v>542882</v>
       </c>
       <c r="R13" t="n">
-        <v>6985997</v>
+        <v>6985834</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118637403</v>
+        <v>118637398</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>90451</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1958,25 +1958,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543018</v>
+        <v>543124</v>
       </c>
       <c r="R14" t="n">
-        <v>6986137</v>
+        <v>6986062</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118637396</v>
+        <v>118637397</v>
       </c>
       <c r="B15" t="n">
-        <v>79565</v>
+        <v>90518</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543007</v>
+        <v>542989</v>
       </c>
       <c r="R15" t="n">
-        <v>6985892</v>
+        <v>6985815</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118637401</v>
+        <v>118637406</v>
       </c>
       <c r="B16" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2162,25 +2162,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543069</v>
+        <v>542918</v>
       </c>
       <c r="R16" t="n">
-        <v>6986146</v>
+        <v>6985972</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118637399</v>
+        <v>118637404</v>
       </c>
       <c r="B17" t="n">
-        <v>90522</v>
+        <v>90469</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2264,25 +2264,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543124</v>
+        <v>542973</v>
       </c>
       <c r="R17" t="n">
-        <v>6986145</v>
+        <v>6986138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118637402</v>
+        <v>118637403</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2366,25 +2366,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>

--- a/artfynd/A 42078-2019 artfynd.xlsx
+++ b/artfynd/A 42078-2019 artfynd.xlsx
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118637399</v>
+        <v>118637406</v>
       </c>
       <c r="B5" t="n">
-        <v>90522</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,25 +1040,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543124</v>
+        <v>542918</v>
       </c>
       <c r="R5" t="n">
-        <v>6986145</v>
+        <v>6985972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118637394</v>
+        <v>118637408</v>
       </c>
       <c r="B6" t="n">
-        <v>78573</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,25 +1142,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542982</v>
+        <v>542882</v>
       </c>
       <c r="R6" t="n">
-        <v>6985997</v>
+        <v>6985834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118637405</v>
+        <v>118637394</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>78580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1244,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542943</v>
+        <v>542982</v>
       </c>
       <c r="R7" t="n">
-        <v>6986128</v>
+        <v>6985997</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118637396</v>
+        <v>118637395</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543007</v>
+        <v>543004</v>
       </c>
       <c r="R8" t="n">
-        <v>6985892</v>
+        <v>6985918</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118637401</v>
+        <v>118637398</v>
       </c>
       <c r="B9" t="n">
-        <v>90504</v>
+        <v>90458</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,21 +1452,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543069</v>
+        <v>543124</v>
       </c>
       <c r="R9" t="n">
-        <v>6986146</v>
+        <v>6986062</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
         <v>118637407</v>
       </c>
       <c r="B10" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118637395</v>
+        <v>118637403</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,25 +1652,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543004</v>
+        <v>543018</v>
       </c>
       <c r="R11" t="n">
-        <v>6985918</v>
+        <v>6986137</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118637402</v>
+        <v>118637404</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>90476</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,25 +1754,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543018</v>
+        <v>542973</v>
       </c>
       <c r="R12" t="n">
-        <v>6986137</v>
+        <v>6986138</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118637408</v>
+        <v>118637399</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>90529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,25 +1856,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542882</v>
+        <v>543124</v>
       </c>
       <c r="R13" t="n">
-        <v>6985834</v>
+        <v>6986145</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118637398</v>
+        <v>118637397</v>
       </c>
       <c r="B14" t="n">
-        <v>90451</v>
+        <v>90525</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543124</v>
+        <v>542989</v>
       </c>
       <c r="R14" t="n">
-        <v>6986062</v>
+        <v>6985815</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118637397</v>
+        <v>118637401</v>
       </c>
       <c r="B15" t="n">
-        <v>90518</v>
+        <v>90511</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542989</v>
+        <v>543069</v>
       </c>
       <c r="R15" t="n">
-        <v>6985815</v>
+        <v>6986146</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118637406</v>
+        <v>118637402</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2162,25 +2162,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542918</v>
+        <v>543018</v>
       </c>
       <c r="R16" t="n">
-        <v>6985972</v>
+        <v>6986137</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118637404</v>
+        <v>118637405</v>
       </c>
       <c r="B17" t="n">
-        <v>90469</v>
+        <v>97853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2264,25 +2264,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542973</v>
+        <v>542943</v>
       </c>
       <c r="R17" t="n">
-        <v>6986138</v>
+        <v>6986128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118637403</v>
+        <v>118637396</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2366,25 +2366,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543018</v>
+        <v>543007</v>
       </c>
       <c r="R18" t="n">
-        <v>6986137</v>
+        <v>6985892</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 42078-2019 artfynd.xlsx
+++ b/artfynd/A 42078-2019 artfynd.xlsx
@@ -1028,7 +1028,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118637406</v>
+        <v>118637403</v>
       </c>
       <c r="B5" t="n">
         <v>97853</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542918</v>
+        <v>543018</v>
       </c>
       <c r="R5" t="n">
-        <v>6985972</v>
+        <v>6986137</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118637408</v>
+        <v>118637401</v>
       </c>
       <c r="B6" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,25 +1142,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542882</v>
+        <v>543069</v>
       </c>
       <c r="R6" t="n">
-        <v>6985834</v>
+        <v>6986146</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118637394</v>
+        <v>118637407</v>
       </c>
       <c r="B7" t="n">
-        <v>78580</v>
+        <v>79572</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1244,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542982</v>
+        <v>542937</v>
       </c>
       <c r="R7" t="n">
-        <v>6985997</v>
+        <v>6985813</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118637395</v>
+        <v>118637404</v>
       </c>
       <c r="B8" t="n">
-        <v>78491</v>
+        <v>90476</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,25 +1346,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543004</v>
+        <v>542973</v>
       </c>
       <c r="R8" t="n">
-        <v>6985918</v>
+        <v>6986138</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118637398</v>
+        <v>118637399</v>
       </c>
       <c r="B9" t="n">
-        <v>90458</v>
+        <v>90529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,21 +1452,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
         <v>543124</v>
       </c>
       <c r="R9" t="n">
-        <v>6986062</v>
+        <v>6986145</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118637407</v>
+        <v>118637397</v>
       </c>
       <c r="B10" t="n">
-        <v>79572</v>
+        <v>90525</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542937</v>
+        <v>542989</v>
       </c>
       <c r="R10" t="n">
-        <v>6985813</v>
+        <v>6985815</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118637403</v>
+        <v>118637396</v>
       </c>
       <c r="B11" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,25 +1652,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543018</v>
+        <v>543007</v>
       </c>
       <c r="R11" t="n">
-        <v>6986137</v>
+        <v>6985892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118637404</v>
+        <v>118637394</v>
       </c>
       <c r="B12" t="n">
-        <v>90476</v>
+        <v>78580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542973</v>
+        <v>542982</v>
       </c>
       <c r="R12" t="n">
-        <v>6986138</v>
+        <v>6985997</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118637399</v>
+        <v>118637398</v>
       </c>
       <c r="B13" t="n">
-        <v>90529</v>
+        <v>90458</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
         <v>543124</v>
       </c>
       <c r="R13" t="n">
-        <v>6986145</v>
+        <v>6986062</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118637397</v>
+        <v>118637406</v>
       </c>
       <c r="B14" t="n">
-        <v>90525</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1958,25 +1958,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542989</v>
+        <v>542918</v>
       </c>
       <c r="R14" t="n">
-        <v>6985815</v>
+        <v>6985972</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118637401</v>
+        <v>118637395</v>
       </c>
       <c r="B15" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543069</v>
+        <v>543004</v>
       </c>
       <c r="R15" t="n">
-        <v>6986146</v>
+        <v>6985918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118637402</v>
+        <v>118637408</v>
       </c>
       <c r="B16" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2162,25 +2162,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543018</v>
+        <v>542882</v>
       </c>
       <c r="R16" t="n">
-        <v>6986137</v>
+        <v>6985834</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118637396</v>
+        <v>118637402</v>
       </c>
       <c r="B18" t="n">
-        <v>79572</v>
+        <v>78491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,21 +2370,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543007</v>
+        <v>543018</v>
       </c>
       <c r="R18" t="n">
-        <v>6985892</v>
+        <v>6986137</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
